--- a/AC_2009/AC_028.xlsx
+++ b/AC_2009/AC_028.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +165,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O228"/>
+  <dimension ref="A1:O230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -506,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -514,7 +598,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>PS_Serial_No</t>
+          <t>PS_Name</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -587,8 +671,10 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>1</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 1</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>139</v>
@@ -634,8 +720,10 @@
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>2</v>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 2</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>69</v>
@@ -681,8 +769,10 @@
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>3</v>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 3</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>107</v>
@@ -728,8 +818,10 @@
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>4</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 4</t>
+        </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>191</v>
@@ -775,8 +867,10 @@
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>5</v>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 5</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>89</v>
@@ -822,8 +916,10 @@
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>6</v>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 6</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>46</v>
@@ -869,8 +965,10 @@
       <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>7</v>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 7</t>
+        </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>133</v>
@@ -916,8 +1014,10 @@
       <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>8</v>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 8</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>251</v>
@@ -963,8 +1063,10 @@
       <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>9</v>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 9</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>353</v>
@@ -1010,8 +1112,10 @@
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>10</v>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 10</t>
+        </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>181</v>
@@ -1057,8 +1161,10 @@
       <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>11</v>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 11</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>121</v>
@@ -1104,8 +1210,10 @@
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>12</v>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 12</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>101</v>
@@ -1151,8 +1259,10 @@
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>13</v>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 13</t>
+        </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>103</v>
@@ -1198,8 +1308,10 @@
       <c r="A19" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>14</v>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 14</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>172</v>
@@ -1245,8 +1357,10 @@
       <c r="A20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>15</v>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 15</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>63</v>
@@ -1292,8 +1406,10 @@
       <c r="A21" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>16</v>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 16</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>53</v>
@@ -1339,8 +1455,10 @@
       <c r="A22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>17</v>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 17</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>181</v>
@@ -1386,8 +1504,10 @@
       <c r="A23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>18</v>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 18</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>80</v>
@@ -1433,8 +1553,10 @@
       <c r="A24" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>19</v>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 19</t>
+        </is>
       </c>
       <c r="C24" s="4" t="n">
         <v>35</v>
@@ -1480,8 +1602,10 @@
       <c r="A25" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>20</v>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 20</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>79</v>
@@ -1527,8 +1651,10 @@
       <c r="A26" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>21</v>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 21</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>116</v>
@@ -1574,8 +1700,10 @@
       <c r="A27" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>22</v>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 22</t>
+        </is>
       </c>
       <c r="C27" s="4" t="n">
         <v>124</v>
@@ -1621,8 +1749,10 @@
       <c r="A28" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>23</v>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 23</t>
+        </is>
       </c>
       <c r="C28" s="4" t="n">
         <v>243</v>
@@ -1668,8 +1798,10 @@
       <c r="A29" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <v>24</v>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 24</t>
+        </is>
       </c>
       <c r="C29" s="4" t="n">
         <v>133</v>
@@ -1715,8 +1847,10 @@
       <c r="A30" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="4" t="n">
-        <v>25</v>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 25</t>
+        </is>
       </c>
       <c r="C30" s="4" t="n">
         <v>84</v>
@@ -1762,8 +1896,10 @@
       <c r="A31" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>26</v>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 26</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
         <v>50</v>
@@ -1809,8 +1945,10 @@
       <c r="A32" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>27</v>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 27</t>
+        </is>
       </c>
       <c r="C32" s="4" t="n">
         <v>101</v>
@@ -1856,8 +1994,10 @@
       <c r="A33" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>28</v>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 28</t>
+        </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>165</v>
@@ -1903,8 +2043,10 @@
       <c r="A34" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="4" t="n">
-        <v>29</v>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 29</t>
+        </is>
       </c>
       <c r="C34" s="4" t="n">
         <v>261</v>
@@ -1950,8 +2092,10 @@
       <c r="A35" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>30</v>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 30</t>
+        </is>
       </c>
       <c r="C35" s="4" t="n">
         <v>109</v>
@@ -1997,8 +2141,10 @@
       <c r="A36" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="4" t="n">
-        <v>31</v>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 31</t>
+        </is>
       </c>
       <c r="C36" s="4" t="n">
         <v>139</v>
@@ -2044,8 +2190,10 @@
       <c r="A37" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="4" t="n">
-        <v>32</v>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 32</t>
+        </is>
       </c>
       <c r="C37" s="4" t="n">
         <v>262</v>
@@ -2091,8 +2239,10 @@
       <c r="A38" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="4" t="n">
-        <v>33</v>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 33</t>
+        </is>
       </c>
       <c r="C38" s="4" t="n">
         <v>199</v>
@@ -2138,8 +2288,10 @@
       <c r="A39" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="4" t="n">
-        <v>34</v>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 34</t>
+        </is>
       </c>
       <c r="C39" s="4" t="n">
         <v>92</v>
@@ -2185,8 +2337,10 @@
       <c r="A40" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="4" t="n">
-        <v>35</v>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 35</t>
+        </is>
       </c>
       <c r="C40" s="4" t="n">
         <v>65</v>
@@ -2232,8 +2386,10 @@
       <c r="A41" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="4" t="n">
-        <v>36</v>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 36</t>
+        </is>
       </c>
       <c r="C41" s="4" t="n">
         <v>65</v>
@@ -2279,8 +2435,10 @@
       <c r="A42" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="4" t="n">
-        <v>37</v>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 37</t>
+        </is>
       </c>
       <c r="C42" s="4" t="n">
         <v>91</v>
@@ -2326,8 +2484,10 @@
       <c r="A43" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="4" t="n">
-        <v>38</v>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 38</t>
+        </is>
       </c>
       <c r="C43" s="4" t="n">
         <v>123</v>
@@ -2373,8 +2533,10 @@
       <c r="A44" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="4" t="n">
-        <v>39</v>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 39</t>
+        </is>
       </c>
       <c r="C44" s="4" t="n">
         <v>71</v>
@@ -2420,8 +2582,10 @@
       <c r="A45" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="4" t="n">
-        <v>40</v>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 40</t>
+        </is>
       </c>
       <c r="C45" s="4" t="n">
         <v>130</v>
@@ -2467,8 +2631,10 @@
       <c r="A46" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="4" t="n">
-        <v>41</v>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 41</t>
+        </is>
       </c>
       <c r="C46" s="4" t="n">
         <v>123</v>
@@ -2514,8 +2680,10 @@
       <c r="A47" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="4" t="n">
-        <v>42</v>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 42</t>
+        </is>
       </c>
       <c r="C47" s="4" t="n">
         <v>138</v>
@@ -2561,8 +2729,10 @@
       <c r="A48" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="4" t="n">
-        <v>43</v>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 43</t>
+        </is>
       </c>
       <c r="C48" s="4" t="n">
         <v>180</v>
@@ -2608,8 +2778,10 @@
       <c r="A49" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>44</v>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 44</t>
+        </is>
       </c>
       <c r="C49" s="4" t="n">
         <v>269</v>
@@ -2655,8 +2827,10 @@
       <c r="A50" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="4" t="n">
-        <v>45</v>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 45</t>
+        </is>
       </c>
       <c r="C50" s="4" t="n">
         <v>122</v>
@@ -2702,8 +2876,10 @@
       <c r="A51" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B51" s="4" t="n">
-        <v>46</v>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 46</t>
+        </is>
       </c>
       <c r="C51" s="4" t="n">
         <v>118</v>
@@ -2749,8 +2925,10 @@
       <c r="A52" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B52" s="4" t="n">
-        <v>47</v>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 47</t>
+        </is>
       </c>
       <c r="C52" s="4" t="n">
         <v>247</v>
@@ -2796,8 +2974,10 @@
       <c r="A53" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B53" s="4" t="n">
-        <v>48</v>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 48</t>
+        </is>
       </c>
       <c r="C53" s="4" t="n">
         <v>106</v>
@@ -2843,8 +3023,10 @@
       <c r="A54" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B54" s="4" t="n">
-        <v>49</v>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 49</t>
+        </is>
       </c>
       <c r="C54" s="4" t="n">
         <v>122</v>
@@ -2890,8 +3072,10 @@
       <c r="A55" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B55" s="4" t="n">
-        <v>50</v>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 50</t>
+        </is>
       </c>
       <c r="C55" s="4" t="n">
         <v>88</v>
@@ -2937,8 +3121,10 @@
       <c r="A56" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B56" s="4" t="n">
-        <v>51</v>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 51</t>
+        </is>
       </c>
       <c r="C56" s="4" t="n">
         <v>99</v>
@@ -2984,8 +3170,10 @@
       <c r="A57" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B57" s="4" t="n">
-        <v>52</v>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 52</t>
+        </is>
       </c>
       <c r="C57" s="4" t="n">
         <v>95</v>
@@ -3031,8 +3219,10 @@
       <c r="A58" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="4" t="n">
-        <v>53</v>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 53</t>
+        </is>
       </c>
       <c r="C58" s="4" t="n">
         <v>247</v>
@@ -3078,8 +3268,10 @@
       <c r="A59" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B59" s="4" t="n">
-        <v>54</v>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 54</t>
+        </is>
       </c>
       <c r="C59" s="4" t="n">
         <v>81</v>
@@ -3125,8 +3317,10 @@
       <c r="A60" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B60" s="4" t="n">
-        <v>55</v>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 55</t>
+        </is>
       </c>
       <c r="C60" s="4" t="n">
         <v>93</v>
@@ -3172,8 +3366,10 @@
       <c r="A61" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B61" s="4" t="n">
-        <v>56</v>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 56</t>
+        </is>
       </c>
       <c r="C61" s="4" t="n">
         <v>168</v>
@@ -3219,8 +3415,10 @@
       <c r="A62" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B62" s="4" t="n">
-        <v>57</v>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 57</t>
+        </is>
       </c>
       <c r="C62" s="4" t="n">
         <v>159</v>
@@ -3266,8 +3464,10 @@
       <c r="A63" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B63" s="4" t="n">
-        <v>58</v>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 58</t>
+        </is>
       </c>
       <c r="C63" s="4" t="n">
         <v>98</v>
@@ -3313,8 +3513,10 @@
       <c r="A64" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B64" s="4" t="n">
-        <v>59</v>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 59</t>
+        </is>
       </c>
       <c r="C64" s="4" t="n">
         <v>101</v>
@@ -3360,8 +3562,10 @@
       <c r="A65" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="4" t="n">
-        <v>60</v>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 60</t>
+        </is>
       </c>
       <c r="C65" s="4" t="n">
         <v>146</v>
@@ -3407,8 +3611,10 @@
       <c r="A66" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B66" s="4" t="n">
-        <v>61</v>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 61</t>
+        </is>
       </c>
       <c r="C66" s="4" t="n">
         <v>218</v>
@@ -3454,8 +3660,10 @@
       <c r="A67" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="4" t="n">
-        <v>62</v>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 62</t>
+        </is>
       </c>
       <c r="C67" s="4" t="n">
         <v>257</v>
@@ -3501,8 +3709,10 @@
       <c r="A68" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B68" s="4" t="n">
-        <v>63</v>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 63</t>
+        </is>
       </c>
       <c r="C68" s="4" t="n">
         <v>271</v>
@@ -3548,8 +3758,10 @@
       <c r="A69" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B69" s="4" t="n">
-        <v>64</v>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 64</t>
+        </is>
       </c>
       <c r="C69" s="4" t="n">
         <v>70</v>
@@ -3595,8 +3807,10 @@
       <c r="A70" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B70" s="4" t="n">
-        <v>65</v>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 65</t>
+        </is>
       </c>
       <c r="C70" s="4" t="n">
         <v>91</v>
@@ -3642,8 +3856,10 @@
       <c r="A71" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B71" s="4" t="n">
-        <v>66</v>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 66</t>
+        </is>
       </c>
       <c r="C71" s="4" t="n">
         <v>75</v>
@@ -3689,8 +3905,10 @@
       <c r="A72" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B72" s="4" t="n">
-        <v>67</v>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 67</t>
+        </is>
       </c>
       <c r="C72" s="4" t="n">
         <v>153</v>
@@ -3736,8 +3954,10 @@
       <c r="A73" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B73" s="4" t="n">
-        <v>68</v>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 68</t>
+        </is>
       </c>
       <c r="C73" s="4" t="n">
         <v>103</v>
@@ -3783,8 +4003,10 @@
       <c r="A74" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B74" s="4" t="n">
-        <v>69</v>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 69</t>
+        </is>
       </c>
       <c r="C74" s="4" t="n">
         <v>111</v>
@@ -3830,8 +4052,10 @@
       <c r="A75" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B75" s="4" t="n">
-        <v>70</v>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 70</t>
+        </is>
       </c>
       <c r="C75" s="4" t="n">
         <v>151</v>
@@ -3877,8 +4101,10 @@
       <c r="A76" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B76" s="4" t="n">
-        <v>71</v>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 71</t>
+        </is>
       </c>
       <c r="C76" s="4" t="n">
         <v>184</v>
@@ -3924,8 +4150,10 @@
       <c r="A77" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>72</v>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 72</t>
+        </is>
       </c>
       <c r="C77" s="4" t="n">
         <v>113</v>
@@ -3971,8 +4199,10 @@
       <c r="A78" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>73</v>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 73</t>
+        </is>
       </c>
       <c r="C78" s="4" t="n">
         <v>127</v>
@@ -4018,8 +4248,10 @@
       <c r="A79" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B79" s="4" t="n">
-        <v>74</v>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 74</t>
+        </is>
       </c>
       <c r="C79" s="4" t="n">
         <v>86</v>
@@ -4065,8 +4297,10 @@
       <c r="A80" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B80" s="4" t="n">
-        <v>75</v>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 75</t>
+        </is>
       </c>
       <c r="C80" s="4" t="n">
         <v>77</v>
@@ -4112,8 +4346,10 @@
       <c r="A81" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B81" s="4" t="n">
-        <v>76</v>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 76</t>
+        </is>
       </c>
       <c r="C81" s="4" t="n">
         <v>186</v>
@@ -4159,8 +4395,10 @@
       <c r="A82" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B82" s="4" t="n">
-        <v>77</v>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 77</t>
+        </is>
       </c>
       <c r="C82" s="4" t="n">
         <v>138</v>
@@ -4206,8 +4444,10 @@
       <c r="A83" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="B83" s="4" t="n">
-        <v>78</v>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 78</t>
+        </is>
       </c>
       <c r="C83" s="4" t="n">
         <v>99</v>
@@ -4253,8 +4493,10 @@
       <c r="A84" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B84" s="4" t="n">
-        <v>79</v>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 79</t>
+        </is>
       </c>
       <c r="C84" s="4" t="n">
         <v>187</v>
@@ -4300,8 +4542,10 @@
       <c r="A85" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="B85" s="4" t="n">
-        <v>80</v>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 80</t>
+        </is>
       </c>
       <c r="C85" s="4" t="n">
         <v>221</v>
@@ -4347,8 +4591,10 @@
       <c r="A86" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="B86" s="4" t="n">
-        <v>81</v>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 81</t>
+        </is>
       </c>
       <c r="C86" s="4" t="n">
         <v>99</v>
@@ -4394,8 +4640,10 @@
       <c r="A87" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="B87" s="4" t="n">
-        <v>82</v>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 82</t>
+        </is>
       </c>
       <c r="C87" s="4" t="n">
         <v>124</v>
@@ -4441,8 +4689,10 @@
       <c r="A88" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="B88" s="4" t="n">
-        <v>83</v>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 83</t>
+        </is>
       </c>
       <c r="C88" s="4" t="n">
         <v>229</v>
@@ -4488,8 +4738,10 @@
       <c r="A89" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B89" s="4" t="n">
-        <v>84</v>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 84</t>
+        </is>
       </c>
       <c r="C89" s="4" t="n">
         <v>152</v>
@@ -4535,8 +4787,10 @@
       <c r="A90" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="B90" s="4" t="n">
-        <v>85</v>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 85</t>
+        </is>
       </c>
       <c r="C90" s="4" t="n">
         <v>154</v>
@@ -4582,8 +4836,10 @@
       <c r="A91" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="B91" s="4" t="n">
-        <v>86</v>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 86</t>
+        </is>
       </c>
       <c r="C91" s="4" t="n">
         <v>86</v>
@@ -4629,8 +4885,10 @@
       <c r="A92" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="B92" s="4" t="n">
-        <v>87</v>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 87</t>
+        </is>
       </c>
       <c r="C92" s="4" t="n">
         <v>185</v>
@@ -4676,8 +4934,10 @@
       <c r="A93" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B93" s="4" t="n">
-        <v>88</v>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 88</t>
+        </is>
       </c>
       <c r="C93" s="4" t="n">
         <v>281</v>
@@ -4723,8 +4983,10 @@
       <c r="A94" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="B94" s="4" t="n">
-        <v>89</v>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 89</t>
+        </is>
       </c>
       <c r="C94" s="4" t="n">
         <v>300</v>
@@ -4770,8 +5032,10 @@
       <c r="A95" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="B95" s="4" t="n">
-        <v>90</v>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 90</t>
+        </is>
       </c>
       <c r="C95" s="4" t="n">
         <v>355</v>
@@ -4817,8 +5081,10 @@
       <c r="A96" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B96" s="4" t="n">
-        <v>91</v>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 91</t>
+        </is>
       </c>
       <c r="C96" s="4" t="n">
         <v>181</v>
@@ -4864,8 +5130,10 @@
       <c r="A97" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>92</v>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 92</t>
+        </is>
       </c>
       <c r="C97" s="4" t="n">
         <v>188</v>
@@ -4911,8 +5179,10 @@
       <c r="A98" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B98" s="4" t="n">
-        <v>93</v>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 93</t>
+        </is>
       </c>
       <c r="C98" s="4" t="n">
         <v>310</v>
@@ -4958,8 +5228,10 @@
       <c r="A99" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B99" s="4" t="n">
-        <v>94</v>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 94</t>
+        </is>
       </c>
       <c r="C99" s="4" t="n">
         <v>259</v>
@@ -5005,8 +5277,10 @@
       <c r="A100" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B100" s="4" t="n">
-        <v>95</v>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 95</t>
+        </is>
       </c>
       <c r="C100" s="4" t="n">
         <v>204</v>
@@ -5052,8 +5326,10 @@
       <c r="A101" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B101" s="4" t="n">
-        <v>96</v>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 96</t>
+        </is>
       </c>
       <c r="C101" s="4" t="n">
         <v>282</v>
@@ -5099,8 +5375,10 @@
       <c r="A102" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="B102" s="4" t="n">
-        <v>97</v>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 97</t>
+        </is>
       </c>
       <c r="C102" s="4" t="n">
         <v>191</v>
@@ -5146,8 +5424,10 @@
       <c r="A103" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="B103" s="4" t="n">
-        <v>98</v>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 98</t>
+        </is>
       </c>
       <c r="C103" s="4" t="n">
         <v>63</v>
@@ -5193,8 +5473,10 @@
       <c r="A104" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B104" s="4" t="n">
-        <v>99</v>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 99</t>
+        </is>
       </c>
       <c r="C104" s="4" t="n">
         <v>274</v>
@@ -5240,8 +5522,10 @@
       <c r="A105" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="B105" s="4" t="n">
-        <v>100</v>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 100</t>
+        </is>
       </c>
       <c r="C105" s="4" t="n">
         <v>276</v>
@@ -5287,8 +5571,10 @@
       <c r="A106" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="B106" s="4" t="n">
-        <v>101</v>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 101</t>
+        </is>
       </c>
       <c r="C106" s="4" t="n">
         <v>139</v>
@@ -5334,8 +5620,10 @@
       <c r="A107" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="B107" s="4" t="n">
-        <v>102</v>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 102</t>
+        </is>
       </c>
       <c r="C107" s="4" t="n">
         <v>173</v>
@@ -5381,8 +5669,10 @@
       <c r="A108" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="B108" s="4" t="n">
-        <v>103</v>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 103</t>
+        </is>
       </c>
       <c r="C108" s="4" t="n">
         <v>118</v>
@@ -5428,8 +5718,10 @@
       <c r="A109" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="B109" s="4" t="n">
-        <v>104</v>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 104</t>
+        </is>
       </c>
       <c r="C109" s="4" t="n">
         <v>283</v>
@@ -5475,8 +5767,10 @@
       <c r="A110" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="B110" s="4" t="n">
-        <v>105</v>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 105</t>
+        </is>
       </c>
       <c r="C110" s="4" t="n">
         <v>190</v>
@@ -5522,8 +5816,10 @@
       <c r="A111" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="B111" s="4" t="n">
-        <v>106</v>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 106</t>
+        </is>
       </c>
       <c r="C111" s="4" t="n">
         <v>294</v>
@@ -5569,8 +5865,10 @@
       <c r="A112" s="4" t="n">
         <v>107</v>
       </c>
-      <c r="B112" s="4" t="n">
-        <v>107</v>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 107</t>
+        </is>
       </c>
       <c r="C112" s="4" t="n">
         <v>198</v>
@@ -5616,8 +5914,10 @@
       <c r="A113" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="B113" s="4" t="n">
-        <v>108</v>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 108</t>
+        </is>
       </c>
       <c r="C113" s="4" t="n">
         <v>163</v>
@@ -5663,8 +5963,10 @@
       <c r="A114" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="B114" s="4" t="n">
-        <v>109</v>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 109</t>
+        </is>
       </c>
       <c r="C114" s="4" t="n">
         <v>98</v>
@@ -5710,8 +6012,10 @@
       <c r="A115" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="B115" s="4" t="n">
-        <v>110</v>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 110</t>
+        </is>
       </c>
       <c r="C115" s="4" t="n">
         <v>164</v>
@@ -5757,8 +6061,10 @@
       <c r="A116" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="B116" s="4" t="n">
-        <v>111</v>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 111</t>
+        </is>
       </c>
       <c r="C116" s="4" t="n">
         <v>142</v>
@@ -5804,8 +6110,10 @@
       <c r="A117" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="B117" s="4" t="n">
-        <v>112</v>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 112</t>
+        </is>
       </c>
       <c r="C117" s="4" t="n">
         <v>77</v>
@@ -5851,8 +6159,10 @@
       <c r="A118" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="B118" s="4" t="n">
-        <v>113</v>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 113</t>
+        </is>
       </c>
       <c r="C118" s="4" t="n">
         <v>65</v>
@@ -5898,8 +6208,10 @@
       <c r="A119" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="B119" s="4" t="n">
-        <v>114</v>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 114</t>
+        </is>
       </c>
       <c r="C119" s="4" t="n">
         <v>220</v>
@@ -5945,8 +6257,10 @@
       <c r="A120" s="4" t="n">
         <v>115</v>
       </c>
-      <c r="B120" s="4" t="n">
-        <v>115</v>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 115</t>
+        </is>
       </c>
       <c r="C120" s="4" t="n">
         <v>255</v>
@@ -5992,8 +6306,10 @@
       <c r="A121" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B121" s="4" t="n">
-        <v>116</v>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 116</t>
+        </is>
       </c>
       <c r="C121" s="4" t="n">
         <v>328</v>
@@ -6039,8 +6355,10 @@
       <c r="A122" s="4" t="n">
         <v>117</v>
       </c>
-      <c r="B122" s="4" t="n">
-        <v>117</v>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 117</t>
+        </is>
       </c>
       <c r="C122" s="4" t="n">
         <v>196</v>
@@ -6086,8 +6404,10 @@
       <c r="A123" s="4" t="n">
         <v>118</v>
       </c>
-      <c r="B123" s="4" t="n">
-        <v>118</v>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 118</t>
+        </is>
       </c>
       <c r="C123" s="4" t="n">
         <v>243</v>
@@ -6133,8 +6453,10 @@
       <c r="A124" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="B124" s="4" t="n">
-        <v>119</v>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 119</t>
+        </is>
       </c>
       <c r="C124" s="4" t="n">
         <v>217</v>
@@ -6180,8 +6502,10 @@
       <c r="A125" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="B125" s="4" t="n">
-        <v>120</v>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 120</t>
+        </is>
       </c>
       <c r="C125" s="4" t="n">
         <v>145</v>
@@ -6227,8 +6551,10 @@
       <c r="A126" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="B126" s="4" t="n">
-        <v>121</v>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 121</t>
+        </is>
       </c>
       <c r="C126" s="4" t="n">
         <v>197</v>
@@ -6274,8 +6600,10 @@
       <c r="A127" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="B127" s="4" t="n">
-        <v>122</v>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 122</t>
+        </is>
       </c>
       <c r="C127" s="4" t="n">
         <v>139</v>
@@ -6321,8 +6649,10 @@
       <c r="A128" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="B128" s="4" t="n">
-        <v>123</v>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 123</t>
+        </is>
       </c>
       <c r="C128" s="4" t="n">
         <v>94</v>
@@ -6368,8 +6698,10 @@
       <c r="A129" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="B129" s="4" t="n">
-        <v>124</v>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 124</t>
+        </is>
       </c>
       <c r="C129" s="4" t="n">
         <v>159</v>
@@ -6415,8 +6747,10 @@
       <c r="A130" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="B130" s="4" t="n">
-        <v>125</v>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 125</t>
+        </is>
       </c>
       <c r="C130" s="4" t="n">
         <v>138</v>
@@ -6462,8 +6796,10 @@
       <c r="A131" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="B131" s="4" t="n">
-        <v>126</v>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 126</t>
+        </is>
       </c>
       <c r="C131" s="4" t="n">
         <v>120</v>
@@ -6509,8 +6845,10 @@
       <c r="A132" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="B132" s="4" t="n">
-        <v>127</v>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 127</t>
+        </is>
       </c>
       <c r="C132" s="4" t="n">
         <v>80</v>
@@ -6556,8 +6894,10 @@
       <c r="A133" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="B133" s="4" t="n">
-        <v>128</v>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 128</t>
+        </is>
       </c>
       <c r="C133" s="4" t="n">
         <v>117</v>
@@ -6603,8 +6943,10 @@
       <c r="A134" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="B134" s="4" t="n">
-        <v>129</v>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 129</t>
+        </is>
       </c>
       <c r="C134" s="4" t="n">
         <v>202</v>
@@ -6650,8 +6992,10 @@
       <c r="A135" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="B135" s="4" t="n">
-        <v>130</v>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 130</t>
+        </is>
       </c>
       <c r="C135" s="4" t="n">
         <v>144</v>
@@ -6697,8 +7041,10 @@
       <c r="A136" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="B136" s="4" t="n">
-        <v>131</v>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 131</t>
+        </is>
       </c>
       <c r="C136" s="4" t="n">
         <v>149</v>
@@ -6744,8 +7090,10 @@
       <c r="A137" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="B137" s="4" t="n">
-        <v>132</v>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 132</t>
+        </is>
       </c>
       <c r="C137" s="4" t="n">
         <v>81</v>
@@ -6791,8 +7139,10 @@
       <c r="A138" s="4" t="n">
         <v>133</v>
       </c>
-      <c r="B138" s="4" t="n">
-        <v>133</v>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 133</t>
+        </is>
       </c>
       <c r="C138" s="4" t="n">
         <v>50</v>
@@ -6838,8 +7188,10 @@
       <c r="A139" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="B139" s="4" t="n">
-        <v>134</v>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 134</t>
+        </is>
       </c>
       <c r="C139" s="4" t="n">
         <v>168</v>
@@ -6885,8 +7237,10 @@
       <c r="A140" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="B140" s="4" t="n">
-        <v>135</v>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 135</t>
+        </is>
       </c>
       <c r="C140" s="4" t="n">
         <v>175</v>
@@ -6932,8 +7286,10 @@
       <c r="A141" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="B141" s="4" t="n">
-        <v>136</v>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 136</t>
+        </is>
       </c>
       <c r="C141" s="4" t="n">
         <v>162</v>
@@ -6979,8 +7335,10 @@
       <c r="A142" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="B142" s="4" t="n">
-        <v>137</v>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 137</t>
+        </is>
       </c>
       <c r="C142" s="4" t="n">
         <v>190</v>
@@ -7026,8 +7384,10 @@
       <c r="A143" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="B143" s="4" t="n">
-        <v>138</v>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 138</t>
+        </is>
       </c>
       <c r="C143" s="4" t="n">
         <v>188</v>
@@ -7073,8 +7433,10 @@
       <c r="A144" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="B144" s="4" t="n">
-        <v>139</v>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 139</t>
+        </is>
       </c>
       <c r="C144" s="4" t="n">
         <v>87</v>
@@ -7120,8 +7482,10 @@
       <c r="A145" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="B145" s="4" t="n">
-        <v>140</v>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 140</t>
+        </is>
       </c>
       <c r="C145" s="4" t="n">
         <v>87</v>
@@ -7167,8 +7531,10 @@
       <c r="A146" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="B146" s="4" t="n">
-        <v>141</v>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 141</t>
+        </is>
       </c>
       <c r="C146" s="4" t="n">
         <v>334</v>
@@ -7214,8 +7580,10 @@
       <c r="A147" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="B147" s="4" t="n">
-        <v>142</v>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 142</t>
+        </is>
       </c>
       <c r="C147" s="4" t="n">
         <v>356</v>
@@ -7261,8 +7629,10 @@
       <c r="A148" s="4" t="n">
         <v>143</v>
       </c>
-      <c r="B148" s="4" t="n">
-        <v>143</v>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 143</t>
+        </is>
       </c>
       <c r="C148" s="4" t="n">
         <v>374</v>
@@ -7308,8 +7678,10 @@
       <c r="A149" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="B149" s="4" t="n">
-        <v>144</v>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 144</t>
+        </is>
       </c>
       <c r="C149" s="4" t="n">
         <v>147</v>
@@ -7355,8 +7727,10 @@
       <c r="A150" s="4" t="n">
         <v>145</v>
       </c>
-      <c r="B150" s="4" t="n">
-        <v>145</v>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 145</t>
+        </is>
       </c>
       <c r="C150" s="4" t="n">
         <v>185</v>
@@ -7402,8 +7776,10 @@
       <c r="A151" s="4" t="n">
         <v>146</v>
       </c>
-      <c r="B151" s="4" t="n">
-        <v>146</v>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 146</t>
+        </is>
       </c>
       <c r="C151" s="4" t="n">
         <v>164</v>
@@ -7449,8 +7825,10 @@
       <c r="A152" s="4" t="n">
         <v>147</v>
       </c>
-      <c r="B152" s="4" t="n">
-        <v>147</v>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 147</t>
+        </is>
       </c>
       <c r="C152" s="4" t="n">
         <v>140</v>
@@ -7496,8 +7874,10 @@
       <c r="A153" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="B153" s="4" t="n">
-        <v>148</v>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 148</t>
+        </is>
       </c>
       <c r="C153" s="4" t="n">
         <v>143</v>
@@ -7543,8 +7923,10 @@
       <c r="A154" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="B154" s="4" t="n">
-        <v>149</v>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 149</t>
+        </is>
       </c>
       <c r="C154" s="4" t="n">
         <v>124</v>
@@ -7590,8 +7972,10 @@
       <c r="A155" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="B155" s="4" t="n">
-        <v>150</v>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 150</t>
+        </is>
       </c>
       <c r="C155" s="4" t="n">
         <v>182</v>
@@ -7637,8 +8021,10 @@
       <c r="A156" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="B156" s="4" t="n">
-        <v>151</v>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 151</t>
+        </is>
       </c>
       <c r="C156" s="4" t="n">
         <v>188</v>
@@ -7684,8 +8070,10 @@
       <c r="A157" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="B157" s="4" t="n">
-        <v>152</v>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 152</t>
+        </is>
       </c>
       <c r="C157" s="4" t="n">
         <v>159</v>
@@ -7731,8 +8119,10 @@
       <c r="A158" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="B158" s="4" t="n">
-        <v>153</v>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 153</t>
+        </is>
       </c>
       <c r="C158" s="4" t="n">
         <v>152</v>
@@ -7778,8 +8168,10 @@
       <c r="A159" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="B159" s="4" t="n">
-        <v>154</v>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 154</t>
+        </is>
       </c>
       <c r="C159" s="4" t="n">
         <v>180</v>
@@ -7825,8 +8217,10 @@
       <c r="A160" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="B160" s="4" t="n">
-        <v>155</v>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 155</t>
+        </is>
       </c>
       <c r="C160" s="4" t="n">
         <v>208</v>
@@ -7872,8 +8266,10 @@
       <c r="A161" s="4" t="n">
         <v>156</v>
       </c>
-      <c r="B161" s="4" t="n">
-        <v>156</v>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 156</t>
+        </is>
       </c>
       <c r="C161" s="4" t="n">
         <v>214</v>
@@ -7919,8 +8315,10 @@
       <c r="A162" s="4" t="n">
         <v>157</v>
       </c>
-      <c r="B162" s="4" t="n">
-        <v>157</v>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 157</t>
+        </is>
       </c>
       <c r="C162" s="4" t="n">
         <v>176</v>
@@ -7966,8 +8364,10 @@
       <c r="A163" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="B163" s="4" t="n">
-        <v>158</v>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 158</t>
+        </is>
       </c>
       <c r="C163" s="4" t="n">
         <v>136</v>
@@ -8013,8 +8413,10 @@
       <c r="A164" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="B164" s="4" t="n">
-        <v>159</v>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 159</t>
+        </is>
       </c>
       <c r="C164" s="4" t="n">
         <v>99</v>
@@ -8060,8 +8462,10 @@
       <c r="A165" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="B165" s="4" t="n">
-        <v>160</v>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 160</t>
+        </is>
       </c>
       <c r="C165" s="4" t="n">
         <v>191</v>
@@ -8107,8 +8511,10 @@
       <c r="A166" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="B166" s="4" t="n">
-        <v>161</v>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 161</t>
+        </is>
       </c>
       <c r="C166" s="4" t="n">
         <v>159</v>
@@ -8154,8 +8560,10 @@
       <c r="A167" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="B167" s="4" t="n">
-        <v>162</v>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 162</t>
+        </is>
       </c>
       <c r="C167" s="4" t="n">
         <v>163</v>
@@ -8201,8 +8609,10 @@
       <c r="A168" s="4" t="n">
         <v>163</v>
       </c>
-      <c r="B168" s="4" t="n">
-        <v>163</v>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 163</t>
+        </is>
       </c>
       <c r="C168" s="4" t="n">
         <v>129</v>
@@ -8248,8 +8658,10 @@
       <c r="A169" s="4" t="n">
         <v>164</v>
       </c>
-      <c r="B169" s="4" t="n">
-        <v>164</v>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 164</t>
+        </is>
       </c>
       <c r="C169" s="4" t="n">
         <v>86</v>
@@ -8295,8 +8707,10 @@
       <c r="A170" s="4" t="n">
         <v>165</v>
       </c>
-      <c r="B170" s="4" t="n">
-        <v>165</v>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 165</t>
+        </is>
       </c>
       <c r="C170" s="4" t="n">
         <v>61</v>
@@ -8342,8 +8756,10 @@
       <c r="A171" s="4" t="n">
         <v>166</v>
       </c>
-      <c r="B171" s="4" t="n">
-        <v>166</v>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 166</t>
+        </is>
       </c>
       <c r="C171" s="4" t="n">
         <v>149</v>
@@ -8389,8 +8805,10 @@
       <c r="A172" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="B172" s="4" t="n">
-        <v>167</v>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 167</t>
+        </is>
       </c>
       <c r="C172" s="4" t="n">
         <v>196</v>
@@ -8436,8 +8854,10 @@
       <c r="A173" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="B173" s="4" t="n">
-        <v>168</v>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 168</t>
+        </is>
       </c>
       <c r="C173" s="4" t="n">
         <v>223</v>
@@ -8483,8 +8903,10 @@
       <c r="A174" s="4" t="n">
         <v>169</v>
       </c>
-      <c r="B174" s="4" t="n">
-        <v>169</v>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 169</t>
+        </is>
       </c>
       <c r="C174" s="4" t="n">
         <v>86</v>
@@ -8530,8 +8952,10 @@
       <c r="A175" s="4" t="n">
         <v>170</v>
       </c>
-      <c r="B175" s="4" t="n">
-        <v>170</v>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 170</t>
+        </is>
       </c>
       <c r="C175" s="4" t="n">
         <v>78</v>
@@ -8577,8 +9001,10 @@
       <c r="A176" s="4" t="n">
         <v>171</v>
       </c>
-      <c r="B176" s="4" t="n">
-        <v>171</v>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 171</t>
+        </is>
       </c>
       <c r="C176" s="4" t="n">
         <v>135</v>
@@ -8624,8 +9050,10 @@
       <c r="A177" s="4" t="n">
         <v>172</v>
       </c>
-      <c r="B177" s="4" t="n">
-        <v>172</v>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 172</t>
+        </is>
       </c>
       <c r="C177" s="4" t="n">
         <v>87</v>
@@ -8671,8 +9099,10 @@
       <c r="A178" s="4" t="n">
         <v>173</v>
       </c>
-      <c r="B178" s="4" t="n">
-        <v>173</v>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 173</t>
+        </is>
       </c>
       <c r="C178" s="4" t="n">
         <v>204</v>
@@ -8718,8 +9148,10 @@
       <c r="A179" s="4" t="n">
         <v>174</v>
       </c>
-      <c r="B179" s="4" t="n">
-        <v>174</v>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 174</t>
+        </is>
       </c>
       <c r="C179" s="4" t="n">
         <v>31</v>
@@ -8765,8 +9197,10 @@
       <c r="A180" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="B180" s="4" t="n">
-        <v>175</v>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 175</t>
+        </is>
       </c>
       <c r="C180" s="4" t="n">
         <v>54</v>
@@ -8812,8 +9246,10 @@
       <c r="A181" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="B181" s="4" t="n">
-        <v>176</v>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 176</t>
+        </is>
       </c>
       <c r="C181" s="4" t="n">
         <v>196</v>
@@ -8859,8 +9295,10 @@
       <c r="A182" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="B182" s="4" t="n">
-        <v>177</v>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 177</t>
+        </is>
       </c>
       <c r="C182" s="4" t="n">
         <v>219</v>
@@ -8906,8 +9344,10 @@
       <c r="A183" s="4" t="n">
         <v>178</v>
       </c>
-      <c r="B183" s="4" t="n">
-        <v>178</v>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 178</t>
+        </is>
       </c>
       <c r="C183" s="4" t="n">
         <v>76</v>
@@ -8953,8 +9393,10 @@
       <c r="A184" s="4" t="n">
         <v>179</v>
       </c>
-      <c r="B184" s="4" t="n">
-        <v>179</v>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 179</t>
+        </is>
       </c>
       <c r="C184" s="4" t="n">
         <v>141</v>
@@ -9000,8 +9442,10 @@
       <c r="A185" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="B185" s="4" t="n">
-        <v>180</v>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 180</t>
+        </is>
       </c>
       <c r="C185" s="4" t="n">
         <v>177</v>
@@ -9047,8 +9491,10 @@
       <c r="A186" s="4" t="n">
         <v>181</v>
       </c>
-      <c r="B186" s="4" t="n">
-        <v>181</v>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 181</t>
+        </is>
       </c>
       <c r="C186" s="4" t="n">
         <v>207</v>
@@ -9094,8 +9540,10 @@
       <c r="A187" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="B187" s="4" t="n">
-        <v>182</v>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 182</t>
+        </is>
       </c>
       <c r="C187" s="4" t="n">
         <v>301</v>
@@ -9141,8 +9589,10 @@
       <c r="A188" s="4" t="n">
         <v>183</v>
       </c>
-      <c r="B188" s="4" t="n">
-        <v>183</v>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 183</t>
+        </is>
       </c>
       <c r="C188" s="4" t="n">
         <v>163</v>
@@ -9188,8 +9638,10 @@
       <c r="A189" s="4" t="n">
         <v>184</v>
       </c>
-      <c r="B189" s="4" t="n">
-        <v>184</v>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 184</t>
+        </is>
       </c>
       <c r="C189" s="4" t="n">
         <v>169</v>
@@ -9235,8 +9687,10 @@
       <c r="A190" s="4" t="n">
         <v>185</v>
       </c>
-      <c r="B190" s="4" t="n">
-        <v>185</v>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 185</t>
+        </is>
       </c>
       <c r="C190" s="4" t="n">
         <v>66</v>
@@ -9282,8 +9736,10 @@
       <c r="A191" s="4" t="n">
         <v>186</v>
       </c>
-      <c r="B191" s="4" t="n">
-        <v>186</v>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 186</t>
+        </is>
       </c>
       <c r="C191" s="4" t="n">
         <v>76</v>
@@ -9329,8 +9785,10 @@
       <c r="A192" s="4" t="n">
         <v>187</v>
       </c>
-      <c r="B192" s="4" t="n">
-        <v>187</v>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 187</t>
+        </is>
       </c>
       <c r="C192" s="4" t="n">
         <v>102</v>
@@ -9376,8 +9834,10 @@
       <c r="A193" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="B193" s="4" t="n">
-        <v>188</v>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 188</t>
+        </is>
       </c>
       <c r="C193" s="4" t="n">
         <v>179</v>
@@ -9423,8 +9883,10 @@
       <c r="A194" s="4" t="n">
         <v>189</v>
       </c>
-      <c r="B194" s="4" t="n">
-        <v>189</v>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 189</t>
+        </is>
       </c>
       <c r="C194" s="4" t="n">
         <v>94</v>
@@ -9470,8 +9932,10 @@
       <c r="A195" s="4" t="n">
         <v>190</v>
       </c>
-      <c r="B195" s="4" t="n">
-        <v>190</v>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 190</t>
+        </is>
       </c>
       <c r="C195" s="4" t="n">
         <v>91</v>
@@ -9517,8 +9981,10 @@
       <c r="A196" s="4" t="n">
         <v>191</v>
       </c>
-      <c r="B196" s="4" t="n">
-        <v>191</v>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 191</t>
+        </is>
       </c>
       <c r="C196" s="4" t="n">
         <v>108</v>
@@ -9564,8 +10030,10 @@
       <c r="A197" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="B197" s="4" t="n">
-        <v>192</v>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 192</t>
+        </is>
       </c>
       <c r="C197" s="4" t="n">
         <v>278</v>
@@ -9611,8 +10079,10 @@
       <c r="A198" s="4" t="n">
         <v>193</v>
       </c>
-      <c r="B198" s="4" t="n">
-        <v>193</v>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 193</t>
+        </is>
       </c>
       <c r="C198" s="4" t="n">
         <v>158</v>
@@ -9658,8 +10128,10 @@
       <c r="A199" s="4" t="n">
         <v>194</v>
       </c>
-      <c r="B199" s="4" t="n">
-        <v>194</v>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 194</t>
+        </is>
       </c>
       <c r="C199" s="4" t="n">
         <v>199</v>
@@ -9705,8 +10177,10 @@
       <c r="A200" s="4" t="n">
         <v>195</v>
       </c>
-      <c r="B200" s="4" t="n">
-        <v>195</v>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 195</t>
+        </is>
       </c>
       <c r="C200" s="4" t="n">
         <v>177</v>
@@ -9752,8 +10226,10 @@
       <c r="A201" s="4" t="n">
         <v>196</v>
       </c>
-      <c r="B201" s="4" t="n">
-        <v>196</v>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 196</t>
+        </is>
       </c>
       <c r="C201" s="4" t="n">
         <v>201</v>
@@ -9799,8 +10275,10 @@
       <c r="A202" s="4" t="n">
         <v>197</v>
       </c>
-      <c r="B202" s="4" t="n">
-        <v>197</v>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 197</t>
+        </is>
       </c>
       <c r="C202" s="4" t="n">
         <v>155</v>
@@ -9846,8 +10324,10 @@
       <c r="A203" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="B203" s="4" t="n">
-        <v>198</v>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 198</t>
+        </is>
       </c>
       <c r="C203" s="4" t="n">
         <v>233</v>
@@ -9893,8 +10373,10 @@
       <c r="A204" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="B204" s="4" t="n">
-        <v>199</v>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 199</t>
+        </is>
       </c>
       <c r="C204" s="4" t="n">
         <v>173</v>
@@ -9940,8 +10422,10 @@
       <c r="A205" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="B205" s="4" t="n">
-        <v>200</v>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 200</t>
+        </is>
       </c>
       <c r="C205" s="4" t="n">
         <v>91</v>
@@ -9987,8 +10471,10 @@
       <c r="A206" s="4" t="n">
         <v>201</v>
       </c>
-      <c r="B206" s="4" t="n">
-        <v>201</v>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 201</t>
+        </is>
       </c>
       <c r="C206" s="4" t="n">
         <v>130</v>
@@ -10034,8 +10520,10 @@
       <c r="A207" s="4" t="n">
         <v>202</v>
       </c>
-      <c r="B207" s="4" t="n">
-        <v>202</v>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 202</t>
+        </is>
       </c>
       <c r="C207" s="4" t="n">
         <v>216</v>
@@ -10081,8 +10569,10 @@
       <c r="A208" s="4" t="n">
         <v>203</v>
       </c>
-      <c r="B208" s="4" t="n">
-        <v>203</v>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 203</t>
+        </is>
       </c>
       <c r="C208" s="4" t="n">
         <v>51</v>
@@ -10128,8 +10618,10 @@
       <c r="A209" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="B209" s="4" t="n">
-        <v>204</v>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 204</t>
+        </is>
       </c>
       <c r="C209" s="4" t="n">
         <v>70</v>
@@ -10175,8 +10667,10 @@
       <c r="A210" s="4" t="n">
         <v>205</v>
       </c>
-      <c r="B210" s="4" t="n">
-        <v>205</v>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 205</t>
+        </is>
       </c>
       <c r="C210" s="4" t="n">
         <v>216</v>
@@ -10222,8 +10716,10 @@
       <c r="A211" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="B211" s="4" t="n">
-        <v>206</v>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 206</t>
+        </is>
       </c>
       <c r="C211" s="4" t="n">
         <v>153</v>
@@ -10269,8 +10765,10 @@
       <c r="A212" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="B212" s="4" t="n">
-        <v>207</v>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 207</t>
+        </is>
       </c>
       <c r="C212" s="4" t="n">
         <v>331</v>
@@ -10316,8 +10814,10 @@
       <c r="A213" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="B213" s="4" t="n">
-        <v>208</v>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 208</t>
+        </is>
       </c>
       <c r="C213" s="4" t="n">
         <v>262</v>
@@ -10363,8 +10863,10 @@
       <c r="A214" s="4" t="n">
         <v>209</v>
       </c>
-      <c r="B214" s="4" t="n">
-        <v>209</v>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 209</t>
+        </is>
       </c>
       <c r="C214" s="4" t="n">
         <v>167</v>
@@ -10410,8 +10912,10 @@
       <c r="A215" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="B215" s="4" t="n">
-        <v>210</v>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 210</t>
+        </is>
       </c>
       <c r="C215" s="4" t="n">
         <v>177</v>
@@ -10457,8 +10961,10 @@
       <c r="A216" s="4" t="n">
         <v>211</v>
       </c>
-      <c r="B216" s="4" t="n">
-        <v>211</v>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 211</t>
+        </is>
       </c>
       <c r="C216" s="4" t="n">
         <v>162</v>
@@ -10504,8 +11010,10 @@
       <c r="A217" s="4" t="n">
         <v>212</v>
       </c>
-      <c r="B217" s="4" t="n">
-        <v>212</v>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 212</t>
+        </is>
       </c>
       <c r="C217" s="4" t="n">
         <v>134</v>
@@ -10551,8 +11059,10 @@
       <c r="A218" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="B218" s="4" t="n">
-        <v>213</v>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 213</t>
+        </is>
       </c>
       <c r="C218" s="4" t="n">
         <v>166</v>
@@ -10598,8 +11108,10 @@
       <c r="A219" s="4" t="n">
         <v>214</v>
       </c>
-      <c r="B219" s="4" t="n">
-        <v>214</v>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 214</t>
+        </is>
       </c>
       <c r="C219" s="4" t="n">
         <v>126</v>
@@ -10645,8 +11157,10 @@
       <c r="A220" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="B220" s="4" t="n">
-        <v>215</v>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 215</t>
+        </is>
       </c>
       <c r="C220" s="4" t="n">
         <v>47</v>
@@ -10692,8 +11206,10 @@
       <c r="A221" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="B221" s="4" t="n">
-        <v>216</v>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 216</t>
+        </is>
       </c>
       <c r="C221" s="4" t="n">
         <v>64</v>
@@ -10739,8 +11255,10 @@
       <c r="A222" s="4" t="n">
         <v>217</v>
       </c>
-      <c r="B222" s="4" t="n">
-        <v>217</v>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 217</t>
+        </is>
       </c>
       <c r="C222" s="4" t="n">
         <v>68</v>
@@ -10786,8 +11304,10 @@
       <c r="A223" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="B223" s="4" t="n">
-        <v>218</v>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 218</t>
+        </is>
       </c>
       <c r="C223" s="4" t="n">
         <v>95</v>
@@ -10833,8 +11353,10 @@
       <c r="A224" s="4" t="n">
         <v>219</v>
       </c>
-      <c r="B224" s="4" t="n">
-        <v>219</v>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 219</t>
+        </is>
       </c>
       <c r="C224" s="4" t="n">
         <v>165</v>
@@ -10880,8 +11402,10 @@
       <c r="A225" s="4" t="n">
         <v>220</v>
       </c>
-      <c r="B225" s="4" t="n">
-        <v>220</v>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 220</t>
+        </is>
       </c>
       <c r="C225" s="4" t="n">
         <v>179</v>
@@ -10927,8 +11451,10 @@
       <c r="A226" s="4" t="n">
         <v>221</v>
       </c>
-      <c r="B226" s="4" t="n">
-        <v>221</v>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 221</t>
+        </is>
       </c>
       <c r="C226" s="4" t="n">
         <v>234</v>
@@ -10974,8 +11500,10 @@
       <c r="A227" s="4" t="n">
         <v>222</v>
       </c>
-      <c r="B227" s="4" t="n">
-        <v>222</v>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 222</t>
+        </is>
       </c>
       <c r="C227" s="4" t="n">
         <v>127</v>
@@ -11018,61 +11546,169 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B228" s="6">
-        <f>SUM(B6:B227)</f>
-        <v/>
-      </c>
-      <c r="C228" s="6">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="inlineStr"/>
+      <c r="C228" s="9">
         <f>SUM(C6:C227)</f>
         <v/>
       </c>
-      <c r="D228" s="6">
+      <c r="D228" s="9">
         <f>SUM(D6:D227)</f>
         <v/>
       </c>
-      <c r="E228" s="6">
+      <c r="E228" s="9">
         <f>SUM(E6:E227)</f>
         <v/>
       </c>
-      <c r="F228" s="6">
+      <c r="F228" s="9">
         <f>SUM(F6:F227)</f>
         <v/>
       </c>
-      <c r="G228" s="6">
+      <c r="G228" s="9">
         <f>SUM(G6:G227)</f>
         <v/>
       </c>
-      <c r="H228" s="6">
+      <c r="H228" s="9">
         <f>SUM(H6:H227)</f>
         <v/>
       </c>
-      <c r="I228" s="6">
+      <c r="I228" s="9">
         <f>SUM(I6:I227)</f>
         <v/>
       </c>
-      <c r="J228" s="6">
+      <c r="J228" s="9">
         <f>SUM(J6:J227)</f>
         <v/>
       </c>
-      <c r="K228" s="6">
+      <c r="K228" s="9">
         <f>SUM(K6:K227)</f>
         <v/>
       </c>
-      <c r="L228" s="6">
+      <c r="L228" s="9">
         <f>SUM(L6:L227)</f>
         <v/>
       </c>
-      <c r="M228" s="6">
+      <c r="M228" s="9">
         <f>SUM(M6:M227)</f>
         <v/>
       </c>
-      <c r="N228" s="6">
+      <c r="N228" s="9">
         <f>SUM(N6:N227)</f>
+        <v/>
+      </c>
+      <c r="O228" s="9">
+        <f>SUM(O6:O227)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B229" s="11" t="inlineStr"/>
+      <c r="C229" s="12" t="n">
+        <v>201</v>
+      </c>
+      <c r="D229" s="12" t="n">
+        <v>119</v>
+      </c>
+      <c r="E229" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F229" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="G229" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H229" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J229" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="12" t="n">
+        <v>461</v>
+      </c>
+      <c r="L229" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M229" s="12" t="n">
+        <v>508</v>
+      </c>
+      <c r="N229" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B230" s="14" t="inlineStr"/>
+      <c r="C230" s="15">
+        <f>C228+C229</f>
+        <v/>
+      </c>
+      <c r="D230" s="15">
+        <f>D228+D229</f>
+        <v/>
+      </c>
+      <c r="E230" s="15">
+        <f>E228+E229</f>
+        <v/>
+      </c>
+      <c r="F230" s="15">
+        <f>F228+F229</f>
+        <v/>
+      </c>
+      <c r="G230" s="15">
+        <f>G228+G229</f>
+        <v/>
+      </c>
+      <c r="H230" s="15">
+        <f>H228+H229</f>
+        <v/>
+      </c>
+      <c r="I230" s="15">
+        <f>I228+I229</f>
+        <v/>
+      </c>
+      <c r="J230" s="15">
+        <f>J228+J229</f>
+        <v/>
+      </c>
+      <c r="K230" s="15">
+        <f>K228+K229</f>
+        <v/>
+      </c>
+      <c r="L230" s="15">
+        <f>L228+L229</f>
+        <v/>
+      </c>
+      <c r="M230" s="15">
+        <f>M228+M229</f>
+        <v/>
+      </c>
+      <c r="N230" s="15">
+        <f>N228+N229</f>
+        <v/>
+      </c>
+      <c r="O230" s="15">
+        <f>O228+O229</f>
         <v/>
       </c>
     </row>

--- a/AC_2009/AC_028.xlsx
+++ b/AC_2009/AC_028.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +194,25 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -589,7 +621,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -11546,168 +11577,168 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="7" t="inlineStr">
+      <c r="A228" s="16" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B228" s="8" t="inlineStr"/>
-      <c r="C228" s="9">
+      <c r="B228" s="17" t="inlineStr"/>
+      <c r="C228" s="18">
         <f>SUM(C6:C227)</f>
         <v/>
       </c>
-      <c r="D228" s="9">
+      <c r="D228" s="18">
         <f>SUM(D6:D227)</f>
         <v/>
       </c>
-      <c r="E228" s="9">
+      <c r="E228" s="18">
         <f>SUM(E6:E227)</f>
         <v/>
       </c>
-      <c r="F228" s="9">
+      <c r="F228" s="18">
         <f>SUM(F6:F227)</f>
         <v/>
       </c>
-      <c r="G228" s="9">
+      <c r="G228" s="18">
         <f>SUM(G6:G227)</f>
         <v/>
       </c>
-      <c r="H228" s="9">
+      <c r="H228" s="18">
         <f>SUM(H6:H227)</f>
         <v/>
       </c>
-      <c r="I228" s="9">
+      <c r="I228" s="18">
         <f>SUM(I6:I227)</f>
         <v/>
       </c>
-      <c r="J228" s="9">
+      <c r="J228" s="18">
         <f>SUM(J6:J227)</f>
         <v/>
       </c>
-      <c r="K228" s="9">
+      <c r="K228" s="18">
         <f>SUM(K6:K227)</f>
         <v/>
       </c>
-      <c r="L228" s="9">
+      <c r="L228" s="18">
         <f>SUM(L6:L227)</f>
         <v/>
       </c>
-      <c r="M228" s="9">
+      <c r="M228" s="18">
         <f>SUM(M6:M227)</f>
         <v/>
       </c>
-      <c r="N228" s="9">
+      <c r="N228" s="18">
         <f>SUM(N6:N227)</f>
         <v/>
       </c>
-      <c r="O228" s="9">
+      <c r="O228" s="18">
         <f>SUM(O6:O227)</f>
         <v/>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="10" t="inlineStr">
+      <c r="A229" s="19" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B229" s="11" t="inlineStr"/>
-      <c r="C229" s="12" t="n">
+      <c r="C229" s="18" t="n">
         <v>201</v>
       </c>
-      <c r="D229" s="12" t="n">
+      <c r="D229" s="18" t="n">
         <v>119</v>
       </c>
-      <c r="E229" s="12" t="n">
+      <c r="E229" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="F229" s="12" t="n">
+      <c r="F229" s="18" t="n">
         <v>93</v>
       </c>
-      <c r="G229" s="12" t="n">
+      <c r="G229" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="H229" s="12" t="n">
+      <c r="H229" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="I229" s="12" t="n">
+      <c r="I229" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="J229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" s="12" t="n">
+      <c r="J229" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="18" t="n">
         <v>461</v>
       </c>
-      <c r="L229" s="12" t="n">
+      <c r="L229" s="18" t="n">
         <v>47</v>
       </c>
-      <c r="M229" s="12" t="n">
+      <c r="M229" s="18" t="n">
         <v>508</v>
       </c>
-      <c r="N229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O229" s="12" t="n">
+      <c r="N229" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="13" t="inlineStr">
+      <c r="A230" s="20" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B230" s="14" t="inlineStr"/>
-      <c r="C230" s="15">
+      <c r="B230" s="21" t="inlineStr"/>
+      <c r="C230" s="22">
         <f>C228+C229</f>
         <v/>
       </c>
-      <c r="D230" s="15">
+      <c r="D230" s="22">
         <f>D228+D229</f>
         <v/>
       </c>
-      <c r="E230" s="15">
+      <c r="E230" s="22">
         <f>E228+E229</f>
         <v/>
       </c>
-      <c r="F230" s="15">
+      <c r="F230" s="22">
         <f>F228+F229</f>
         <v/>
       </c>
-      <c r="G230" s="15">
+      <c r="G230" s="22">
         <f>G228+G229</f>
         <v/>
       </c>
-      <c r="H230" s="15">
+      <c r="H230" s="22">
         <f>H228+H229</f>
         <v/>
       </c>
-      <c r="I230" s="15">
+      <c r="I230" s="22">
         <f>I228+I229</f>
         <v/>
       </c>
-      <c r="J230" s="15">
+      <c r="J230" s="22">
         <f>J228+J229</f>
         <v/>
       </c>
-      <c r="K230" s="15">
+      <c r="K230" s="22">
         <f>K228+K229</f>
         <v/>
       </c>
-      <c r="L230" s="15">
+      <c r="L230" s="22">
         <f>L228+L229</f>
         <v/>
       </c>
-      <c r="M230" s="15">
+      <c r="M230" s="22">
         <f>M228+M229</f>
         <v/>
       </c>
-      <c r="N230" s="15">
+      <c r="N230" s="22">
         <f>N228+N229</f>
         <v/>
       </c>
-      <c r="O230" s="15">
+      <c r="O230" s="22">
         <f>O228+O229</f>
         <v/>
       </c>

--- a/AC_2009/AC_028.xlsx
+++ b/AC_2009/AC_028.xlsx
@@ -1462,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O230"/>
+  <dimension ref="A1:N230"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" style="1" min="1" max="1"/>
@@ -1477,8 +1477,7 @@
     <col width="17" customWidth="1" style="1" min="12" max="12"/>
     <col width="16" customWidth="1" style="1" min="13" max="13"/>
     <col width="17" customWidth="1" style="1" min="14" max="14"/>
-    <col width="16" customWidth="1" style="1" min="15" max="15"/>
-    <col width="8.851559999999999" customWidth="1" style="1" min="16" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.35" customHeight="1" s="23">
@@ -1500,7 +1499,6 @@
       <c r="L1" s="3" t="n"/>
       <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
-      <c r="O1" s="3" t="n"/>
     </row>
     <row r="2" ht="13.75" customHeight="1" s="23">
       <c r="A2" s="4" t="inlineStr">
@@ -1521,7 +1519,6 @@
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
     </row>
     <row r="3" ht="13.75" customHeight="1" s="23">
       <c r="A3" s="4" t="inlineStr">
@@ -1542,7 +1539,6 @@
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
     </row>
     <row r="4" ht="13.55" customHeight="1" s="23">
       <c r="A4" s="5" t="n"/>
@@ -1559,7 +1555,6 @@
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
       <c r="N4" s="5" t="n"/>
-      <c r="O4" s="5" t="n"/>
     </row>
     <row r="5" ht="13.55" customHeight="1" s="23">
       <c r="A5" s="6" t="inlineStr">
@@ -1627,14 +1622,9 @@
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>Checksum_Diff</t>
         </is>
       </c>
     </row>
@@ -1683,9 +1673,6 @@
       <c r="N6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" ht="13.55" customHeight="1" s="23">
       <c r="A7" s="9" t="n">
@@ -1732,9 +1719,6 @@
       <c r="N7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" ht="13.55" customHeight="1" s="23">
       <c r="A8" s="9" t="n">
@@ -1781,9 +1765,6 @@
       <c r="N8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" ht="13.55" customHeight="1" s="23">
       <c r="A9" s="9" t="n">
@@ -1830,9 +1811,6 @@
       <c r="N9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="23">
       <c r="A10" s="9" t="n">
@@ -1879,9 +1857,6 @@
       <c r="N10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11" ht="13.55" customHeight="1" s="23">
       <c r="A11" s="9" t="n">
@@ -1928,9 +1903,6 @@
       <c r="N11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" ht="13.55" customHeight="1" s="23">
       <c r="A12" s="9" t="n">
@@ -1977,9 +1949,6 @@
       <c r="N12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="23">
       <c r="A13" s="9" t="n">
@@ -2026,9 +1995,6 @@
       <c r="N13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="13.55" customHeight="1" s="23">
       <c r="A14" s="9" t="n">
@@ -2075,9 +2041,6 @@
       <c r="N14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" ht="13.55" customHeight="1" s="23">
       <c r="A15" s="9" t="n">
@@ -2124,9 +2087,6 @@
       <c r="N15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" ht="13.55" customHeight="1" s="23">
       <c r="A16" s="9" t="n">
@@ -2173,9 +2133,6 @@
       <c r="N16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" ht="13.55" customHeight="1" s="23">
       <c r="A17" s="9" t="n">
@@ -2222,9 +2179,6 @@
       <c r="N17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" ht="13.55" customHeight="1" s="23">
       <c r="A18" s="9" t="n">
@@ -2271,9 +2225,6 @@
       <c r="N18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" ht="13.55" customHeight="1" s="23">
       <c r="A19" s="9" t="n">
@@ -2320,9 +2271,6 @@
       <c r="N19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" ht="13.55" customHeight="1" s="23">
       <c r="A20" s="9" t="n">
@@ -2369,9 +2317,6 @@
       <c r="N20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" ht="13.55" customHeight="1" s="23">
       <c r="A21" s="9" t="n">
@@ -2418,9 +2363,6 @@
       <c r="N21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" ht="13.55" customHeight="1" s="23">
       <c r="A22" s="9" t="n">
@@ -2467,9 +2409,6 @@
       <c r="N22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23" ht="13.55" customHeight="1" s="23">
       <c r="A23" s="9" t="n">
@@ -2516,9 +2455,6 @@
       <c r="N23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" ht="13.55" customHeight="1" s="23">
       <c r="A24" s="9" t="n">
@@ -2565,9 +2501,6 @@
       <c r="N24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" ht="13.55" customHeight="1" s="23">
       <c r="A25" s="9" t="n">
@@ -2614,9 +2547,6 @@
       <c r="N25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" ht="13.55" customHeight="1" s="23">
       <c r="A26" s="9" t="n">
@@ -2663,9 +2593,6 @@
       <c r="N26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" ht="13.55" customHeight="1" s="23">
       <c r="A27" s="9" t="n">
@@ -2712,9 +2639,6 @@
       <c r="N27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28" ht="13.55" customHeight="1" s="23">
       <c r="A28" s="9" t="n">
@@ -2761,9 +2685,6 @@
       <c r="N28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29" ht="13.55" customHeight="1" s="23">
       <c r="A29" s="9" t="n">
@@ -2810,9 +2731,6 @@
       <c r="N29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30" ht="13.55" customHeight="1" s="23">
       <c r="A30" s="9" t="n">
@@ -2859,9 +2777,6 @@
       <c r="N30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31" ht="13.55" customHeight="1" s="23">
       <c r="A31" s="9" t="n">
@@ -2908,9 +2823,6 @@
       <c r="N31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32" ht="13.55" customHeight="1" s="23">
       <c r="A32" s="9" t="n">
@@ -2957,9 +2869,6 @@
       <c r="N32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33" ht="13.55" customHeight="1" s="23">
       <c r="A33" s="9" t="n">
@@ -3006,9 +2915,6 @@
       <c r="N33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" ht="13.55" customHeight="1" s="23">
       <c r="A34" s="9" t="n">
@@ -3055,9 +2961,6 @@
       <c r="N34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35" ht="13.55" customHeight="1" s="23">
       <c r="A35" s="9" t="n">
@@ -3104,9 +3007,6 @@
       <c r="N35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" ht="13.55" customHeight="1" s="23">
       <c r="A36" s="9" t="n">
@@ -3153,9 +3053,6 @@
       <c r="N36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" ht="13.55" customHeight="1" s="23">
       <c r="A37" s="9" t="n">
@@ -3202,9 +3099,6 @@
       <c r="N37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" ht="13.55" customHeight="1" s="23">
       <c r="A38" s="9" t="n">
@@ -3251,9 +3145,6 @@
       <c r="N38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" ht="13.55" customHeight="1" s="23">
       <c r="A39" s="9" t="n">
@@ -3300,9 +3191,6 @@
       <c r="N39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40" ht="13.55" customHeight="1" s="23">
       <c r="A40" s="9" t="n">
@@ -3349,9 +3237,6 @@
       <c r="N40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41" ht="13.55" customHeight="1" s="23">
       <c r="A41" s="9" t="n">
@@ -3398,9 +3283,6 @@
       <c r="N41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42" ht="13.55" customHeight="1" s="23">
       <c r="A42" s="9" t="n">
@@ -3447,9 +3329,6 @@
       <c r="N42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43" ht="13.55" customHeight="1" s="23">
       <c r="A43" s="9" t="n">
@@ -3496,9 +3375,6 @@
       <c r="N43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44" ht="13.55" customHeight="1" s="23">
       <c r="A44" s="9" t="n">
@@ -3545,9 +3421,6 @@
       <c r="N44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" ht="13.55" customHeight="1" s="23">
       <c r="A45" s="9" t="n">
@@ -3594,9 +3467,6 @@
       <c r="N45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" ht="13.55" customHeight="1" s="23">
       <c r="A46" s="9" t="n">
@@ -3643,9 +3513,6 @@
       <c r="N46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="47" ht="13.55" customHeight="1" s="23">
       <c r="A47" s="9" t="n">
@@ -3692,9 +3559,6 @@
       <c r="N47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O47" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="48" ht="13.55" customHeight="1" s="23">
       <c r="A48" s="9" t="n">
@@ -3741,9 +3605,6 @@
       <c r="N48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O48" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49" ht="13.55" customHeight="1" s="23">
       <c r="A49" s="9" t="n">
@@ -3790,9 +3651,6 @@
       <c r="N49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O49" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="50" ht="13.55" customHeight="1" s="23">
       <c r="A50" s="9" t="n">
@@ -3839,9 +3697,6 @@
       <c r="N50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O50" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="51" ht="13.55" customHeight="1" s="23">
       <c r="A51" s="9" t="n">
@@ -3888,9 +3743,6 @@
       <c r="N51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O51" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="52" ht="13.55" customHeight="1" s="23">
       <c r="A52" s="9" t="n">
@@ -3937,9 +3789,6 @@
       <c r="N52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O52" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="53" ht="13.55" customHeight="1" s="23">
       <c r="A53" s="9" t="n">
@@ -3986,9 +3835,6 @@
       <c r="N53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="54" ht="13.55" customHeight="1" s="23">
       <c r="A54" s="9" t="n">
@@ -4035,9 +3881,6 @@
       <c r="N54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O54" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="55" ht="13.55" customHeight="1" s="23">
       <c r="A55" s="9" t="n">
@@ -4084,9 +3927,6 @@
       <c r="N55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O55" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56" ht="13.55" customHeight="1" s="23">
       <c r="A56" s="9" t="n">
@@ -4133,9 +3973,6 @@
       <c r="N56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O56" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57" ht="13.55" customHeight="1" s="23">
       <c r="A57" s="9" t="n">
@@ -4182,9 +4019,6 @@
       <c r="N57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58" ht="13.55" customHeight="1" s="23">
       <c r="A58" s="9" t="n">
@@ -4231,9 +4065,6 @@
       <c r="N58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O58" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59" ht="13.55" customHeight="1" s="23">
       <c r="A59" s="9" t="n">
@@ -4280,9 +4111,6 @@
       <c r="N59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O59" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60" ht="13.55" customHeight="1" s="23">
       <c r="A60" s="9" t="n">
@@ -4329,9 +4157,6 @@
       <c r="N60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O60" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61" ht="13.55" customHeight="1" s="23">
       <c r="A61" s="9" t="n">
@@ -4378,9 +4203,6 @@
       <c r="N61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O61" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62" ht="13.55" customHeight="1" s="23">
       <c r="A62" s="9" t="n">
@@ -4427,9 +4249,6 @@
       <c r="N62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O62" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63" ht="13.55" customHeight="1" s="23">
       <c r="A63" s="9" t="n">
@@ -4476,9 +4295,6 @@
       <c r="N63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O63" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64" ht="13.55" customHeight="1" s="23">
       <c r="A64" s="9" t="n">
@@ -4525,9 +4341,6 @@
       <c r="N64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O64" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65" ht="13.55" customHeight="1" s="23">
       <c r="A65" s="9" t="n">
@@ -4574,9 +4387,6 @@
       <c r="N65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O65" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="66" ht="13.55" customHeight="1" s="23">
       <c r="A66" s="9" t="n">
@@ -4623,9 +4433,6 @@
       <c r="N66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O66" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67" ht="13.55" customHeight="1" s="23">
       <c r="A67" s="9" t="n">
@@ -4672,9 +4479,6 @@
       <c r="N67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O67" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68" ht="13.55" customHeight="1" s="23">
       <c r="A68" s="9" t="n">
@@ -4721,9 +4525,6 @@
       <c r="N68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O68" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69" ht="13.55" customHeight="1" s="23">
       <c r="A69" s="9" t="n">
@@ -4770,9 +4571,6 @@
       <c r="N69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O69" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="70" ht="13.55" customHeight="1" s="23">
       <c r="A70" s="9" t="n">
@@ -4819,9 +4617,6 @@
       <c r="N70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O70" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71" ht="13.55" customHeight="1" s="23">
       <c r="A71" s="9" t="n">
@@ -4868,9 +4663,6 @@
       <c r="N71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O71" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="72" ht="13.55" customHeight="1" s="23">
       <c r="A72" s="9" t="n">
@@ -4917,9 +4709,6 @@
       <c r="N72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O72" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73" ht="13.55" customHeight="1" s="23">
       <c r="A73" s="9" t="n">
@@ -4966,9 +4755,6 @@
       <c r="N73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O73" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74" ht="13.55" customHeight="1" s="23">
       <c r="A74" s="9" t="n">
@@ -5015,9 +4801,6 @@
       <c r="N74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O74" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" ht="13.55" customHeight="1" s="23">
       <c r="A75" s="9" t="n">
@@ -5064,9 +4847,6 @@
       <c r="N75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O75" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" ht="13.55" customHeight="1" s="23">
       <c r="A76" s="9" t="n">
@@ -5113,9 +4893,6 @@
       <c r="N76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O76" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" ht="13.55" customHeight="1" s="23">
       <c r="A77" s="9" t="n">
@@ -5162,9 +4939,6 @@
       <c r="N77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O77" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78" ht="13.55" customHeight="1" s="23">
       <c r="A78" s="9" t="n">
@@ -5211,9 +4985,6 @@
       <c r="N78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O78" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79" ht="13.55" customHeight="1" s="23">
       <c r="A79" s="9" t="n">
@@ -5260,9 +5031,6 @@
       <c r="N79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O79" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80" ht="13.55" customHeight="1" s="23">
       <c r="A80" s="9" t="n">
@@ -5309,9 +5077,6 @@
       <c r="N80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O80" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81" ht="13.55" customHeight="1" s="23">
       <c r="A81" s="9" t="n">
@@ -5358,9 +5123,6 @@
       <c r="N81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O81" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82" ht="13.55" customHeight="1" s="23">
       <c r="A82" s="9" t="n">
@@ -5407,9 +5169,6 @@
       <c r="N82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O82" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83" ht="13.55" customHeight="1" s="23">
       <c r="A83" s="9" t="n">
@@ -5456,9 +5215,6 @@
       <c r="N83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O83" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84" ht="13.55" customHeight="1" s="23">
       <c r="A84" s="9" t="n">
@@ -5505,9 +5261,6 @@
       <c r="N84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O84" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="85" ht="13.55" customHeight="1" s="23">
       <c r="A85" s="9" t="n">
@@ -5554,9 +5307,6 @@
       <c r="N85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O85" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="86" ht="13.55" customHeight="1" s="23">
       <c r="A86" s="9" t="n">
@@ -5603,9 +5353,6 @@
       <c r="N86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O86" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="87" ht="13.55" customHeight="1" s="23">
       <c r="A87" s="9" t="n">
@@ -5652,9 +5399,6 @@
       <c r="N87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O87" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88" ht="13.55" customHeight="1" s="23">
       <c r="A88" s="9" t="n">
@@ -5701,9 +5445,6 @@
       <c r="N88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O88" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="89" ht="13.55" customHeight="1" s="23">
       <c r="A89" s="9" t="n">
@@ -5750,9 +5491,6 @@
       <c r="N89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="90" ht="13.55" customHeight="1" s="23">
       <c r="A90" s="9" t="n">
@@ -5799,9 +5537,6 @@
       <c r="N90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O90" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="91" ht="13.55" customHeight="1" s="23">
       <c r="A91" s="9" t="n">
@@ -5848,9 +5583,6 @@
       <c r="N91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O91" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92" ht="13.55" customHeight="1" s="23">
       <c r="A92" s="9" t="n">
@@ -5897,9 +5629,6 @@
       <c r="N92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O92" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="93" ht="13.55" customHeight="1" s="23">
       <c r="A93" s="9" t="n">
@@ -5946,9 +5675,6 @@
       <c r="N93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O93" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94" ht="13.55" customHeight="1" s="23">
       <c r="A94" s="9" t="n">
@@ -5995,9 +5721,6 @@
       <c r="N94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O94" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="95" ht="13.55" customHeight="1" s="23">
       <c r="A95" s="9" t="n">
@@ -6044,9 +5767,6 @@
       <c r="N95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O95" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96" ht="13.55" customHeight="1" s="23">
       <c r="A96" s="9" t="n">
@@ -6093,9 +5813,6 @@
       <c r="N96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O96" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="97" ht="13.55" customHeight="1" s="23">
       <c r="A97" s="9" t="n">
@@ -6142,9 +5859,6 @@
       <c r="N97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O97" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="98" ht="13.55" customHeight="1" s="23">
       <c r="A98" s="9" t="n">
@@ -6191,9 +5905,6 @@
       <c r="N98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O98" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99" ht="13.55" customHeight="1" s="23">
       <c r="A99" s="9" t="n">
@@ -6240,9 +5951,6 @@
       <c r="N99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O99" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100" ht="13.55" customHeight="1" s="23">
       <c r="A100" s="9" t="n">
@@ -6289,9 +5997,6 @@
       <c r="N100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O100" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="101" ht="13.55" customHeight="1" s="23">
       <c r="A101" s="9" t="n">
@@ -6338,9 +6043,6 @@
       <c r="N101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O101" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102" ht="13.55" customHeight="1" s="23">
       <c r="A102" s="9" t="n">
@@ -6387,9 +6089,6 @@
       <c r="N102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O102" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="103" ht="13.55" customHeight="1" s="23">
       <c r="A103" s="9" t="n">
@@ -6436,9 +6135,6 @@
       <c r="N103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O103" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="104" ht="13.55" customHeight="1" s="23">
       <c r="A104" s="9" t="n">
@@ -6485,9 +6181,6 @@
       <c r="N104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O104" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="105" ht="13.55" customHeight="1" s="23">
       <c r="A105" s="9" t="n">
@@ -6534,9 +6227,6 @@
       <c r="N105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O105" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="106" ht="13.55" customHeight="1" s="23">
       <c r="A106" s="9" t="n">
@@ -6583,9 +6273,6 @@
       <c r="N106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O106" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="107" ht="13.55" customHeight="1" s="23">
       <c r="A107" s="9" t="n">
@@ -6632,9 +6319,6 @@
       <c r="N107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O107" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="108" ht="13.55" customHeight="1" s="23">
       <c r="A108" s="9" t="n">
@@ -6681,9 +6365,6 @@
       <c r="N108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O108" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="109" ht="13.55" customHeight="1" s="23">
       <c r="A109" s="9" t="n">
@@ -6730,9 +6411,6 @@
       <c r="N109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O109" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="110" ht="13.55" customHeight="1" s="23">
       <c r="A110" s="9" t="n">
@@ -6779,9 +6457,6 @@
       <c r="N110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O110" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="111" ht="13.55" customHeight="1" s="23">
       <c r="A111" s="9" t="n">
@@ -6828,9 +6503,6 @@
       <c r="N111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O111" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="112" ht="13.55" customHeight="1" s="23">
       <c r="A112" s="9" t="n">
@@ -6877,9 +6549,6 @@
       <c r="N112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O112" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="113" ht="13.55" customHeight="1" s="23">
       <c r="A113" s="9" t="n">
@@ -6926,9 +6595,6 @@
       <c r="N113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O113" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114" ht="13.55" customHeight="1" s="23">
       <c r="A114" s="9" t="n">
@@ -6975,9 +6641,6 @@
       <c r="N114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O114" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115" ht="13.55" customHeight="1" s="23">
       <c r="A115" s="9" t="n">
@@ -7024,9 +6687,6 @@
       <c r="N115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O115" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="116" ht="13.55" customHeight="1" s="23">
       <c r="A116" s="9" t="n">
@@ -7073,9 +6733,6 @@
       <c r="N116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O116" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="117" ht="13.55" customHeight="1" s="23">
       <c r="A117" s="9" t="n">
@@ -7122,9 +6779,6 @@
       <c r="N117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="118" ht="13.55" customHeight="1" s="23">
       <c r="A118" s="9" t="n">
@@ -7171,9 +6825,6 @@
       <c r="N118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O118" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="119" ht="13.55" customHeight="1" s="23">
       <c r="A119" s="9" t="n">
@@ -7220,9 +6871,6 @@
       <c r="N119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O119" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120" ht="13.55" customHeight="1" s="23">
       <c r="A120" s="9" t="n">
@@ -7269,9 +6917,6 @@
       <c r="N120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O120" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="121" ht="13.55" customHeight="1" s="23">
       <c r="A121" s="9" t="n">
@@ -7318,9 +6963,6 @@
       <c r="N121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O121" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122" ht="13.55" customHeight="1" s="23">
       <c r="A122" s="9" t="n">
@@ -7367,9 +7009,6 @@
       <c r="N122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O122" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123" ht="13.55" customHeight="1" s="23">
       <c r="A123" s="9" t="n">
@@ -7416,9 +7055,6 @@
       <c r="N123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O123" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124" ht="13.55" customHeight="1" s="23">
       <c r="A124" s="9" t="n">
@@ -7465,9 +7101,6 @@
       <c r="N124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O124" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="125" ht="13.55" customHeight="1" s="23">
       <c r="A125" s="9" t="n">
@@ -7514,9 +7147,6 @@
       <c r="N125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O125" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="126" ht="13.55" customHeight="1" s="23">
       <c r="A126" s="9" t="n">
@@ -7563,9 +7193,6 @@
       <c r="N126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O126" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="127" ht="13.55" customHeight="1" s="23">
       <c r="A127" s="9" t="n">
@@ -7612,9 +7239,6 @@
       <c r="N127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O127" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="128" ht="13.55" customHeight="1" s="23">
       <c r="A128" s="9" t="n">
@@ -7661,9 +7285,6 @@
       <c r="N128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O128" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129" ht="13.55" customHeight="1" s="23">
       <c r="A129" s="9" t="n">
@@ -7710,9 +7331,6 @@
       <c r="N129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O129" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="130" ht="13.55" customHeight="1" s="23">
       <c r="A130" s="9" t="n">
@@ -7759,9 +7377,6 @@
       <c r="N130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O130" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="131" ht="13.55" customHeight="1" s="23">
       <c r="A131" s="9" t="n">
@@ -7808,9 +7423,6 @@
       <c r="N131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O131" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="132" ht="13.55" customHeight="1" s="23">
       <c r="A132" s="9" t="n">
@@ -7857,9 +7469,6 @@
       <c r="N132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O132" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="133" ht="13.55" customHeight="1" s="23">
       <c r="A133" s="9" t="n">
@@ -7906,9 +7515,6 @@
       <c r="N133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O133" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="134" ht="13.55" customHeight="1" s="23">
       <c r="A134" s="9" t="n">
@@ -7955,9 +7561,6 @@
       <c r="N134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O134" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="135" ht="13.55" customHeight="1" s="23">
       <c r="A135" s="9" t="n">
@@ -8004,9 +7607,6 @@
       <c r="N135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O135" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="136" ht="13.55" customHeight="1" s="23">
       <c r="A136" s="9" t="n">
@@ -8053,9 +7653,6 @@
       <c r="N136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O136" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137" ht="13.55" customHeight="1" s="23">
       <c r="A137" s="9" t="n">
@@ -8102,9 +7699,6 @@
       <c r="N137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O137" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="138" ht="13.55" customHeight="1" s="23">
       <c r="A138" s="9" t="n">
@@ -8151,9 +7745,6 @@
       <c r="N138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O138" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="139" ht="13.55" customHeight="1" s="23">
       <c r="A139" s="9" t="n">
@@ -8200,9 +7791,6 @@
       <c r="N139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O139" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="140" ht="13.55" customHeight="1" s="23">
       <c r="A140" s="9" t="n">
@@ -8249,9 +7837,6 @@
       <c r="N140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O140" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="141" ht="13.55" customHeight="1" s="23">
       <c r="A141" s="9" t="n">
@@ -8298,9 +7883,6 @@
       <c r="N141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O141" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="142" ht="13.55" customHeight="1" s="23">
       <c r="A142" s="9" t="n">
@@ -8347,9 +7929,6 @@
       <c r="N142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O142" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="143" ht="13.55" customHeight="1" s="23">
       <c r="A143" s="9" t="n">
@@ -8396,9 +7975,6 @@
       <c r="N143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O143" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="144" ht="13.55" customHeight="1" s="23">
       <c r="A144" s="9" t="n">
@@ -8445,9 +8021,6 @@
       <c r="N144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O144" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="145" ht="13.55" customHeight="1" s="23">
       <c r="A145" s="9" t="n">
@@ -8494,9 +8067,6 @@
       <c r="N145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O145" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="146" ht="13.55" customHeight="1" s="23">
       <c r="A146" s="9" t="n">
@@ -8543,9 +8113,6 @@
       <c r="N146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O146" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="147" ht="13.55" customHeight="1" s="23">
       <c r="A147" s="9" t="n">
@@ -8592,9 +8159,6 @@
       <c r="N147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O147" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="148" ht="13.55" customHeight="1" s="23">
       <c r="A148" s="9" t="n">
@@ -8641,9 +8205,6 @@
       <c r="N148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O148" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="149" ht="13.55" customHeight="1" s="23">
       <c r="A149" s="9" t="n">
@@ -8690,9 +8251,6 @@
       <c r="N149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O149" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="150" ht="13.55" customHeight="1" s="23">
       <c r="A150" s="9" t="n">
@@ -8739,9 +8297,6 @@
       <c r="N150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O150" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="151" ht="13.55" customHeight="1" s="23">
       <c r="A151" s="9" t="n">
@@ -8788,9 +8343,6 @@
       <c r="N151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O151" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="152" ht="13.55" customHeight="1" s="23">
       <c r="A152" s="9" t="n">
@@ -8837,9 +8389,6 @@
       <c r="N152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O152" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="153" ht="13.55" customHeight="1" s="23">
       <c r="A153" s="9" t="n">
@@ -8886,9 +8435,6 @@
       <c r="N153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O153" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="154" ht="13.55" customHeight="1" s="23">
       <c r="A154" s="9" t="n">
@@ -8935,9 +8481,6 @@
       <c r="N154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O154" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="155" ht="13.55" customHeight="1" s="23">
       <c r="A155" s="9" t="n">
@@ -8984,9 +8527,6 @@
       <c r="N155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O155" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="156" ht="13.55" customHeight="1" s="23">
       <c r="A156" s="9" t="n">
@@ -9033,9 +8573,6 @@
       <c r="N156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O156" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="157" ht="13.55" customHeight="1" s="23">
       <c r="A157" s="9" t="n">
@@ -9082,9 +8619,6 @@
       <c r="N157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O157" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="158" ht="13.55" customHeight="1" s="23">
       <c r="A158" s="9" t="n">
@@ -9131,9 +8665,6 @@
       <c r="N158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O158" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="159" ht="13.55" customHeight="1" s="23">
       <c r="A159" s="9" t="n">
@@ -9180,9 +8711,6 @@
       <c r="N159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O159" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="160" ht="13.55" customHeight="1" s="23">
       <c r="A160" s="9" t="n">
@@ -9229,9 +8757,6 @@
       <c r="N160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O160" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="161" ht="13.55" customHeight="1" s="23">
       <c r="A161" s="9" t="n">
@@ -9278,9 +8803,6 @@
       <c r="N161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O161" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="162" ht="13.55" customHeight="1" s="23">
       <c r="A162" s="9" t="n">
@@ -9327,9 +8849,6 @@
       <c r="N162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O162" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="163" ht="13.55" customHeight="1" s="23">
       <c r="A163" s="9" t="n">
@@ -9376,9 +8895,6 @@
       <c r="N163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O163" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="164" ht="13.55" customHeight="1" s="23">
       <c r="A164" s="9" t="n">
@@ -9425,9 +8941,6 @@
       <c r="N164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O164" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="165" ht="13.55" customHeight="1" s="23">
       <c r="A165" s="9" t="n">
@@ -9474,9 +8987,6 @@
       <c r="N165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O165" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="166" ht="13.55" customHeight="1" s="23">
       <c r="A166" s="9" t="n">
@@ -9523,9 +9033,6 @@
       <c r="N166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O166" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="167" ht="13.55" customHeight="1" s="23">
       <c r="A167" s="9" t="n">
@@ -9572,9 +9079,6 @@
       <c r="N167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O167" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="168" ht="13.55" customHeight="1" s="23">
       <c r="A168" s="9" t="n">
@@ -9621,9 +9125,6 @@
       <c r="N168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O168" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="169" ht="13.55" customHeight="1" s="23">
       <c r="A169" s="9" t="n">
@@ -9670,9 +9171,6 @@
       <c r="N169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O169" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="170" ht="13.55" customHeight="1" s="23">
       <c r="A170" s="9" t="n">
@@ -9719,9 +9217,6 @@
       <c r="N170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O170" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="171" ht="13.55" customHeight="1" s="23">
       <c r="A171" s="9" t="n">
@@ -9768,9 +9263,6 @@
       <c r="N171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O171" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="172" ht="13.55" customHeight="1" s="23">
       <c r="A172" s="9" t="n">
@@ -9817,9 +9309,6 @@
       <c r="N172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O172" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="173" ht="13.55" customHeight="1" s="23">
       <c r="A173" s="9" t="n">
@@ -9866,9 +9355,6 @@
       <c r="N173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O173" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="174" ht="13.55" customHeight="1" s="23">
       <c r="A174" s="9" t="n">
@@ -9915,9 +9401,6 @@
       <c r="N174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O174" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="175" ht="13.55" customHeight="1" s="23">
       <c r="A175" s="9" t="n">
@@ -9964,9 +9447,6 @@
       <c r="N175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O175" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="176" ht="13.55" customHeight="1" s="23">
       <c r="A176" s="9" t="n">
@@ -10013,9 +9493,6 @@
       <c r="N176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O176" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="177" ht="13.55" customHeight="1" s="23">
       <c r="A177" s="9" t="n">
@@ -10062,9 +9539,6 @@
       <c r="N177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O177" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="178" ht="13.55" customHeight="1" s="23">
       <c r="A178" s="9" t="n">
@@ -10111,9 +9585,6 @@
       <c r="N178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O178" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="179" ht="13.55" customHeight="1" s="23">
       <c r="A179" s="9" t="n">
@@ -10160,9 +9631,6 @@
       <c r="N179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O179" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="180" ht="13.55" customHeight="1" s="23">
       <c r="A180" s="9" t="n">
@@ -10209,9 +9677,6 @@
       <c r="N180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O180" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="181" ht="13.55" customHeight="1" s="23">
       <c r="A181" s="9" t="n">
@@ -10258,9 +9723,6 @@
       <c r="N181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O181" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="182" ht="13.55" customHeight="1" s="23">
       <c r="A182" s="9" t="n">
@@ -10307,9 +9769,6 @@
       <c r="N182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O182" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="183" ht="13.55" customHeight="1" s="23">
       <c r="A183" s="9" t="n">
@@ -10356,9 +9815,6 @@
       <c r="N183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O183" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="184" ht="13.55" customHeight="1" s="23">
       <c r="A184" s="9" t="n">
@@ -10405,9 +9861,6 @@
       <c r="N184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O184" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="185" ht="13.55" customHeight="1" s="23">
       <c r="A185" s="9" t="n">
@@ -10454,9 +9907,6 @@
       <c r="N185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O185" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="186" ht="13.55" customHeight="1" s="23">
       <c r="A186" s="9" t="n">
@@ -10503,9 +9953,6 @@
       <c r="N186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O186" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="187" ht="13.55" customHeight="1" s="23">
       <c r="A187" s="9" t="n">
@@ -10552,9 +9999,6 @@
       <c r="N187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O187" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="188" ht="13.55" customHeight="1" s="23">
       <c r="A188" s="9" t="n">
@@ -10601,9 +10045,6 @@
       <c r="N188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O188" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="189" ht="13.55" customHeight="1" s="23">
       <c r="A189" s="9" t="n">
@@ -10650,9 +10091,6 @@
       <c r="N189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O189" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="190" ht="13.55" customHeight="1" s="23">
       <c r="A190" s="9" t="n">
@@ -10699,9 +10137,6 @@
       <c r="N190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O190" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="191" ht="13.55" customHeight="1" s="23">
       <c r="A191" s="9" t="n">
@@ -10748,9 +10183,6 @@
       <c r="N191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O191" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="192" ht="13.55" customHeight="1" s="23">
       <c r="A192" s="9" t="n">
@@ -10797,9 +10229,6 @@
       <c r="N192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O192" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="193" ht="13.55" customHeight="1" s="23">
       <c r="A193" s="9" t="n">
@@ -10846,9 +10275,6 @@
       <c r="N193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O193" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="194" ht="13.55" customHeight="1" s="23">
       <c r="A194" s="9" t="n">
@@ -10895,9 +10321,6 @@
       <c r="N194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O194" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="195" ht="13.55" customHeight="1" s="23">
       <c r="A195" s="9" t="n">
@@ -10944,9 +10367,6 @@
       <c r="N195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O195" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="196" ht="13.55" customHeight="1" s="23">
       <c r="A196" s="9" t="n">
@@ -10993,9 +10413,6 @@
       <c r="N196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O196" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="197" ht="13.55" customHeight="1" s="23">
       <c r="A197" s="9" t="n">
@@ -11042,9 +10459,6 @@
       <c r="N197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O197" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="198" ht="13.55" customHeight="1" s="23">
       <c r="A198" s="9" t="n">
@@ -11091,9 +10505,6 @@
       <c r="N198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O198" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="199" ht="13.55" customHeight="1" s="23">
       <c r="A199" s="9" t="n">
@@ -11140,9 +10551,6 @@
       <c r="N199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O199" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="200" ht="13.55" customHeight="1" s="23">
       <c r="A200" s="9" t="n">
@@ -11189,9 +10597,6 @@
       <c r="N200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O200" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="201" ht="13.55" customHeight="1" s="23">
       <c r="A201" s="9" t="n">
@@ -11238,9 +10643,6 @@
       <c r="N201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O201" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="202" ht="13.55" customHeight="1" s="23">
       <c r="A202" s="9" t="n">
@@ -11287,9 +10689,6 @@
       <c r="N202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O202" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="203" ht="13.55" customHeight="1" s="23">
       <c r="A203" s="9" t="n">
@@ -11336,9 +10735,6 @@
       <c r="N203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O203" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="204" ht="13.55" customHeight="1" s="23">
       <c r="A204" s="9" t="n">
@@ -11385,9 +10781,6 @@
       <c r="N204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O204" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="205" ht="13.55" customHeight="1" s="23">
       <c r="A205" s="9" t="n">
@@ -11434,9 +10827,6 @@
       <c r="N205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O205" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="206" ht="13.55" customHeight="1" s="23">
       <c r="A206" s="9" t="n">
@@ -11483,9 +10873,6 @@
       <c r="N206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O206" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="207" ht="13.55" customHeight="1" s="23">
       <c r="A207" s="9" t="n">
@@ -11532,9 +10919,6 @@
       <c r="N207" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O207" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="208" ht="13.55" customHeight="1" s="23">
       <c r="A208" s="9" t="n">
@@ -11581,9 +10965,6 @@
       <c r="N208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O208" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="209" ht="13.55" customHeight="1" s="23">
       <c r="A209" s="9" t="n">
@@ -11630,9 +11011,6 @@
       <c r="N209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O209" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="210" ht="13.55" customHeight="1" s="23">
       <c r="A210" s="9" t="n">
@@ -11679,9 +11057,6 @@
       <c r="N210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O210" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="211" ht="13.55" customHeight="1" s="23">
       <c r="A211" s="9" t="n">
@@ -11728,9 +11103,6 @@
       <c r="N211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O211" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="212" ht="13.55" customHeight="1" s="23">
       <c r="A212" s="9" t="n">
@@ -11777,9 +11149,6 @@
       <c r="N212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O212" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="213" ht="13.55" customHeight="1" s="23">
       <c r="A213" s="9" t="n">
@@ -11826,9 +11195,6 @@
       <c r="N213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O213" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="214" ht="13.55" customHeight="1" s="23">
       <c r="A214" s="9" t="n">
@@ -11875,9 +11241,6 @@
       <c r="N214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O214" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="215" ht="13.55" customHeight="1" s="23">
       <c r="A215" s="9" t="n">
@@ -11924,9 +11287,6 @@
       <c r="N215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O215" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="216" ht="13.55" customHeight="1" s="23">
       <c r="A216" s="9" t="n">
@@ -11973,9 +11333,6 @@
       <c r="N216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O216" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="217" ht="13.55" customHeight="1" s="23">
       <c r="A217" s="9" t="n">
@@ -12022,9 +11379,6 @@
       <c r="N217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O217" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="218" ht="13.55" customHeight="1" s="23">
       <c r="A218" s="9" t="n">
@@ -12071,9 +11425,6 @@
       <c r="N218" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O218" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="219" ht="13.55" customHeight="1" s="23">
       <c r="A219" s="9" t="n">
@@ -12120,9 +11471,6 @@
       <c r="N219" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O219" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="220" ht="13.55" customHeight="1" s="23">
       <c r="A220" s="9" t="n">
@@ -12169,9 +11517,6 @@
       <c r="N220" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O220" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="221" ht="13.55" customHeight="1" s="23">
       <c r="A221" s="9" t="n">
@@ -12218,9 +11563,6 @@
       <c r="N221" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O221" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="222" ht="13.55" customHeight="1" s="23">
       <c r="A222" s="9" t="n">
@@ -12267,9 +11609,6 @@
       <c r="N222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O222" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="223" ht="13.55" customHeight="1" s="23">
       <c r="A223" s="9" t="n">
@@ -12316,9 +11655,6 @@
       <c r="N223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O223" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="224" ht="13.55" customHeight="1" s="23">
       <c r="A224" s="9" t="n">
@@ -12365,9 +11701,6 @@
       <c r="N224" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O224" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="225" ht="13.55" customHeight="1" s="23">
       <c r="A225" s="9" t="n">
@@ -12414,9 +11747,6 @@
       <c r="N225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O225" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="226" ht="13.55" customHeight="1" s="23">
       <c r="A226" s="9" t="n">
@@ -12463,9 +11793,6 @@
       <c r="N226" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O226" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="227" ht="14.05" customHeight="1" s="23">
       <c r="A227" s="11" t="n">
@@ -12512,9 +11839,6 @@
       <c r="N227" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="O227" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="228" ht="14.15" customHeight="1" s="23">
       <c r="A228" s="13" t="inlineStr">
@@ -12559,9 +11883,6 @@
       <c r="N228" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O228" s="15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="229" ht="13.65" customHeight="1" s="23">
       <c r="A229" s="16" t="inlineStr">
@@ -12606,9 +11927,6 @@
       <c r="N229" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="O229" s="15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="230" ht="13.65" customHeight="1" s="23">
       <c r="A230" s="18" t="inlineStr">
@@ -12650,10 +11968,7 @@
       <c r="M230" s="21" t="n">
         <v>122142</v>
       </c>
-      <c r="N230" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O230" s="22" t="n">
+      <c r="N230" s="22" t="n">
         <v>0</v>
       </c>
     </row>
